--- a/sample/bom_new.xlsx
+++ b/sample/bom_new.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -437,6 +437,11 @@
           <t>개수</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>조립조건</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -457,6 +462,11 @@
       <c r="D2" t="n">
         <v>3</v>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -477,6 +487,11 @@
       <c r="D3" t="n">
         <v>4</v>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -497,6 +512,11 @@
       <c r="D4" t="n">
         <v>2</v>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -517,6 +537,11 @@
       <c r="D5" t="n">
         <v>1</v>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -536,6 +561,86 @@
       </c>
       <c r="D6" t="n">
         <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Common</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ASSY-COLOR-BCC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SMP-1001</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>WASHER-SPACER 8mm</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>4</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>C_OCOL=BCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ASSY-COLOR-DSC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SMP-1002</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>BOLT M8x20</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>C_OCOL=DSC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ASSY-OPTX-A</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SMP-1005</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>COVER UNDER</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>C_X=A</t>
+        </is>
       </c>
     </row>
   </sheetData>
